--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-nationality.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:49:03+00:00</t>
+    <t>2024-01-29T09:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-nationality.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-nationality.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="136">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:55:21+00:00</t>
+    <t>2024-01-29T12:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -388,6 +388,12 @@
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/country</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -772,7 +778,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="33.2421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1686,13 +1692,11 @@
         <v>76</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Y9" s="2"/>
       <c r="Z9" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>76</v>
@@ -1710,7 +1714,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -1722,7 +1726,7 @@
         <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>100</v>
@@ -1730,13 +1734,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -1761,10 +1765,10 @@
         <v>92</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1835,7 +1839,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>106</v>
@@ -1938,7 +1942,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>108</v>
@@ -2041,7 +2045,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>111</v>
@@ -2084,7 +2088,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>76</v>
@@ -2146,7 +2150,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>118</v>
@@ -2172,7 +2176,7 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>120</v>
@@ -2229,7 +2233,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2241,7 +2245,7 @@
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>100</v>
@@ -2354,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2380,7 +2384,7 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>120</v>
@@ -2437,7 +2441,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2449,7 +2453,7 @@
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>100</v>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-nationality.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:33:53+00:00</t>
+    <t>2024-01-29T12:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-nationality.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-patient-nationality.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:36:14+00:00</t>
+    <t>2024-01-29T12:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -393,7 +393,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/country</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-Country</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -778,7 +778,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="33.2421875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="44.3828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
